--- a/output/graficos_dimensiones/comunal_e_supbrut_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supbrut_a_2023_antofagasta.xlsx
@@ -54,12 +54,12 @@
     <t xml:space="preserve">Sierra Gorda</t>
   </si>
   <si>
+    <t xml:space="preserve">Ollagüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
-    <t xml:space="preserve">Ollagüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:35</t>
+    <t xml:space="preserve">2026-09-10 00:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -618,7 +618,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2302</v>
+        <v>2202</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -631,7 +631,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2202</v>
+        <v>2302</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_supbrut_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supbrut_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:43</t>
+    <t xml:space="preserve">2026-09-18 10:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
